--- a/data/trans_dic/IP11-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP11-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han sufrido algún accidente por el cual necesitase asiscencia sanitaria en los últimos 12 meses.</t>
+          <t>Menores que han sufrido algún accidente por el cual necesitase asiscencia sanitaria en los últimos 12 meses. (tasa de respuesta: 99,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,55; 8,99</t>
+          <t>1,67; 9,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,98; 9,32</t>
+          <t>1,53; 8,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 9,8</t>
+          <t>1,05; 10,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,97</t>
+          <t>0,0; 6,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,8; 8,78</t>
+          <t>0,92; 7,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,18; 22,43</t>
+          <t>8,63; 22,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,94; 8,35</t>
+          <t>0,95; 8,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,71</t>
+          <t>0,0; 10,6</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,91; 6,78</t>
+          <t>1,92; 6,78</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,98; 13,68</t>
+          <t>5,92; 13,37</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,9; 7,38</t>
+          <t>1,86; 7,56</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 6,36</t>
+          <t>0,39; 6,8</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,55; 6,91</t>
+          <t>3,56; 7,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,34; 10,54</t>
+          <t>6,32; 10,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,34; 5,23</t>
+          <t>2,27; 4,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,36; 4,0</t>
+          <t>1,48; 4,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,07; 9,99</t>
+          <t>5,96; 9,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,11; 11,47</t>
+          <t>6,95; 11,51</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,88; 8,43</t>
+          <t>4,81; 8,44</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,72; 4,24</t>
+          <t>1,76; 4,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,11; 7,77</t>
+          <t>5,33; 8,03</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,37; 10,34</t>
+          <t>7,4; 10,57</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,87; 6,21</t>
+          <t>4,07; 6,35</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,88; 3,67</t>
+          <t>1,91; 3,67</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,42; 9,7</t>
+          <t>3,21; 9,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,31; 9,61</t>
+          <t>3,41; 9,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,06; 4,94</t>
+          <t>1,07; 5,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,54; 6,84</t>
+          <t>1,54; 6,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,1; 7,57</t>
+          <t>2,19; 7,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,11; 13,59</t>
+          <t>6,23; 13,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,76; 6,27</t>
+          <t>1,8; 6,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,17; 8,42</t>
+          <t>2,22; 8,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,35; 7,13</t>
+          <t>3,25; 7,16</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,53; 10,48</t>
+          <t>5,42; 10,04</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,92; 4,88</t>
+          <t>1,84; 4,75</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,25; 6,2</t>
+          <t>2,38; 6,48</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,85; 6,65</t>
+          <t>3,99; 6,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,81; 8,93</t>
+          <t>5,82; 8,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,3; 4,48</t>
+          <t>2,42; 4,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,68; 3,81</t>
+          <t>1,66; 3,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,07; 8,08</t>
+          <t>5,06; 8,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,97; 11,52</t>
+          <t>8,2; 11,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,12; 7,04</t>
+          <t>4,21; 7,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,14; 4,62</t>
+          <t>2,17; 4,55</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,85; 6,83</t>
+          <t>4,79; 6,86</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,34; 9,67</t>
+          <t>7,39; 9,88</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,64; 5,45</t>
+          <t>3,62; 5,35</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,16; 3,8</t>
+          <t>2,15; 3,73</t>
         </is>
       </c>
     </row>
@@ -1215,4 +1216,995 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han sufrido algún accidente por el cual necesitase asiscencia sanitaria en los últimos 12 meses. (tasa de respuesta: 99,87%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>4114</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4053</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2457</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1082</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2839</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>12584</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2529</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1350</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>6954</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>16637</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>4986</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>2432</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>1516; 8419</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1415; 8219</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>625; 5975</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3676</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>799; 6742</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>7441; 19230</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>650; 5746</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 6574</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>3413; 12046</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>10567; 23869</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>2375; 9671</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>456; 7935</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>21046</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>37951</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>16500</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>11019</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>36922</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>44894</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>31390</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>14746</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>57968</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>82845</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>47890</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>25765</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>14815; 29247</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>28551; 48298</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>10712; 23228</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>6815; 18543</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>28424; 47088</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>34271; 56729</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>23458; 41191</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>9098; 22566</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>47588; 71677</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>69866; 99817</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>39038; 60950</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>18672; 35757</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>10144</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>9708</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4412</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>5051</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>6764</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>15899</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>6805</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>7937</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>16908</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>25607</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>11218</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>12988</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>5591; 16194</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5688; 15891</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1837; 8828</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2302; 9946</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>3466; 11642</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>10675; 23441</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>3371; 11648</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>4078; 14793</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>10802; 23798</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>18352; 33978</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>6595; 17003</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>7907; 21579</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>35304</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>51712</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>23369</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>17151</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>46525</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>73377</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>40724</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>24034</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>81829</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>125089</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>64093</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>41185</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>27177; 45823</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>41383; 63152</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>16956; 32398</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>11007; 24390</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>36516; 57759</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>61571; 87877</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>31315; 52415</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>16495; 34648</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>67138; 96180</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>107955; 144451</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>52335; 77356</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>30636; 53122</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP11-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP11-Estudios-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,67; 9,26</t>
+          <t>2,13; 9,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,53; 8,9</t>
+          <t>1,52; 8,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,05; 10,06</t>
+          <t>1,03; 9,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,72</t>
+          <t>0,0; 7,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,92; 7,76</t>
+          <t>0,91; 7,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,63; 22,31</t>
+          <t>8,92; 22,41</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,95; 8,37</t>
+          <t>0,95; 9,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,6</t>
+          <t>0,0; 9,83</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,92; 6,78</t>
+          <t>1,98; 7,26</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,92; 13,37</t>
+          <t>6,22; 13,9</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,86; 7,56</t>
+          <t>1,82; 7,3</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,39; 6,8</t>
+          <t>0,54; 6,64</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,56; 7,03</t>
+          <t>3,52; 6,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,32; 10,69</t>
+          <t>6,45; 10,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,27; 4,92</t>
+          <t>2,28; 5,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,48; 4,03</t>
+          <t>1,35; 3,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,96; 9,87</t>
+          <t>5,9; 9,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,95; 11,51</t>
+          <t>7,11; 11,45</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,81; 8,44</t>
+          <t>4,8; 8,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,76; 4,38</t>
+          <t>1,85; 4,37</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,33; 8,03</t>
+          <t>5,32; 7,85</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,4; 10,57</t>
+          <t>7,32; 10,38</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,07; 6,35</t>
+          <t>3,89; 6,17</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,91; 3,67</t>
+          <t>1,86; 3,75</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,21; 9,3</t>
+          <t>3,36; 9,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,41; 9,53</t>
+          <t>3,17; 9,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 5,16</t>
+          <t>1,06; 5,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,54; 6,65</t>
+          <t>1,54; 6,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,19; 7,36</t>
+          <t>2,1; 7,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,23; 13,67</t>
+          <t>5,94; 13,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,8; 6,23</t>
+          <t>1,84; 6,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,22; 8,07</t>
+          <t>2,13; 8,61</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,25; 7,16</t>
+          <t>3,33; 7,38</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,42; 10,04</t>
+          <t>5,46; 10,27</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,84; 4,75</t>
+          <t>1,91; 4,83</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,38; 6,48</t>
+          <t>2,27; 6,27</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,99; 6,73</t>
+          <t>3,85; 6,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,82; 8,88</t>
+          <t>5,71; 9,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,42; 4,61</t>
+          <t>2,45; 4,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,66; 3,67</t>
+          <t>1,65; 3,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,06; 8,0</t>
+          <t>5,11; 8,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,2; 11,71</t>
+          <t>8,13; 11,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,21; 7,05</t>
+          <t>4,22; 7,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,17; 4,55</t>
+          <t>2,15; 4,61</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,79; 6,86</t>
+          <t>4,81; 6,87</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,39; 9,88</t>
+          <t>7,4; 9,83</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,62; 5,35</t>
+          <t>3,65; 5,32</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,15; 3,73</t>
+          <t>2,16; 3,71</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1516; 8419</t>
+          <t>1932; 8401</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1415; 8219</t>
+          <t>1405; 7692</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>625; 5975</t>
+          <t>611; 5824</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3676</t>
+          <t>0; 4244</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>799; 6742</t>
+          <t>794; 6890</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7441; 19230</t>
+          <t>7691; 19318</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>650; 5746</t>
+          <t>654; 6400</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 6574</t>
+          <t>0; 6094</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3413; 12046</t>
+          <t>3520; 12905</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10567; 23869</t>
+          <t>11107; 24821</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2375; 9671</t>
+          <t>2332; 9346</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>456; 7935</t>
+          <t>634; 7753</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14815; 29247</t>
+          <t>14630; 28973</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>28551; 48298</t>
+          <t>29146; 49528</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10712; 23228</t>
+          <t>10743; 23715</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6815; 18543</t>
+          <t>6204; 17037</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>28424; 47088</t>
+          <t>28141; 47135</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34271; 56729</t>
+          <t>35030; 56439</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23458; 41191</t>
+          <t>23405; 40687</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9098; 22566</t>
+          <t>9540; 22548</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>47588; 71677</t>
+          <t>47516; 70129</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>69866; 99817</t>
+          <t>69164; 98062</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>39038; 60950</t>
+          <t>37335; 59181</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18672; 35757</t>
+          <t>18146; 36541</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5591; 16194</t>
+          <t>5848; 16210</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5688; 15891</t>
+          <t>5282; 15416</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1837; 8828</t>
+          <t>1820; 8925</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2302; 9946</t>
+          <t>2304; 10100</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3466; 11642</t>
+          <t>3325; 11911</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10675; 23441</t>
+          <t>10192; 22899</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3371; 11648</t>
+          <t>3444; 12307</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4078; 14793</t>
+          <t>3905; 15791</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10802; 23798</t>
+          <t>11062; 24525</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18352; 33978</t>
+          <t>18478; 34730</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6595; 17003</t>
+          <t>6852; 17283</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7907; 21579</t>
+          <t>7546; 20873</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>27177; 45823</t>
+          <t>26187; 45694</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>41383; 63152</t>
+          <t>40579; 65077</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16956; 32398</t>
+          <t>17224; 31776</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11007; 24390</t>
+          <t>10971; 24898</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>36516; 57759</t>
+          <t>36863; 58823</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>61571; 87877</t>
+          <t>60991; 86973</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31315; 52415</t>
+          <t>31377; 52052</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>16495; 34648</t>
+          <t>16368; 35058</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>67138; 96180</t>
+          <t>67454; 96435</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>107955; 144451</t>
+          <t>108165; 143608</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>52335; 77356</t>
+          <t>52697; 76910</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>30636; 53122</t>
+          <t>30701; 52871</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP11-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP11-Estudios-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3,27%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>14,6%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3,69%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>4,53%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>4,39%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>4,14%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,98%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3,27%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>14,6%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,69%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,13; 9,25</t>
+          <t>0,8; 8,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,52; 8,33</t>
+          <t>9,18; 22,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,03; 9,81</t>
+          <t>0,94; 8,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,76</t>
+          <t>0,0; 10,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,91; 7,93</t>
+          <t>1,55; 8,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,92; 22,41</t>
+          <t>1,98; 9,32</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,95; 9,33</t>
+          <t>1,18; 9,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,83</t>
+          <t>0,0; 9,43</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,98; 7,26</t>
+          <t>1,91; 6,78</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,22; 13,9</t>
+          <t>5,98; 13,68</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,82; 7,3</t>
+          <t>1,9; 7,38</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,54; 6,64</t>
+          <t>0,37; 6,45</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>7,74%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>9,11%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>6,43%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2,89%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>5,06%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>8,4%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>3,5%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2,4%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>7,74%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>9,11%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>6,43%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,52; 6,96</t>
+          <t>6,07; 9,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,45; 10,96</t>
+          <t>7,11; 11,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,28; 5,03</t>
+          <t>4,88; 8,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,71</t>
+          <t>1,75; 4,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,9; 9,88</t>
+          <t>3,55; 6,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,11; 11,45</t>
+          <t>6,34; 10,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,8; 8,34</t>
+          <t>2,34; 5,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,85; 4,37</t>
+          <t>1,46; 4,04</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,32; 7,85</t>
+          <t>5,11; 7,77</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,32; 10,38</t>
+          <t>7,37; 10,34</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,89; 6,17</t>
+          <t>3,87; 6,21</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,86; 3,75</t>
+          <t>1,9; 3,81</t>
         </is>
       </c>
     </row>
@@ -929,44 +929,44 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>4,28%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9,27%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3,64%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4,38%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>5,83%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>5,82%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>2,58%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>3,38%</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>4,28%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>9,27%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3,64%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>4,33%</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
           <t>5,09%</t>
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,36; 9,31</t>
+          <t>2,1; 7,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,17; 9,24</t>
+          <t>6,11; 13,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,06; 5,22</t>
+          <t>1,76; 6,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,54; 6,75</t>
+          <t>2,2; 8,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,1; 7,53</t>
+          <t>3,42; 9,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,94; 13,35</t>
+          <t>3,31; 9,61</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,84; 6,59</t>
+          <t>1,06; 4,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,13; 8,61</t>
+          <t>1,51; 6,91</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,33; 7,38</t>
+          <t>3,35; 7,13</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,46; 10,27</t>
+          <t>5,53; 10,48</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,83</t>
+          <t>1,92; 4,88</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,27; 6,27</t>
+          <t>2,24; 6,33</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6,44%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9,78%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5,48%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3,18%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>5,18%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>7,27%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>3,33%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2,58%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>6,44%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>9,78%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,48%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,85; 6,71</t>
+          <t>5,07; 8,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,71; 9,15</t>
+          <t>7,97; 11,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,45; 4,53</t>
+          <t>4,12; 7,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,65; 3,75</t>
+          <t>2,14; 4,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,11; 8,15</t>
+          <t>3,85; 6,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,13; 11,59</t>
+          <t>5,81; 8,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,22; 7,0</t>
+          <t>2,3; 4,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,15; 4,61</t>
+          <t>1,84; 4,14</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,81; 6,87</t>
+          <t>4,85; 6,83</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,4; 9,83</t>
+          <t>7,34; 9,67</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,65; 5,32</t>
+          <t>3,64; 5,45</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,16; 3,71</t>
+          <t>2,21; 3,87</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1368,42 +1368,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1436,42 +1436,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2839</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>12584</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2529</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>4114</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>4053</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>2457</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1082</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2839</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>12584</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>2529</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2432</t>
+          <t>2266</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1932; 8401</t>
+          <t>692; 7624</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1405; 7692</t>
+          <t>7913; 19329</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>611; 5824</t>
+          <t>645; 5731</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4244</t>
+          <t>0; 5711</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>794; 6890</t>
+          <t>1409; 8165</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7691; 19318</t>
+          <t>1828; 8608</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>654; 6400</t>
+          <t>702; 5816</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 6094</t>
+          <t>0; 4411</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3520; 12905</t>
+          <t>3403; 12055</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11107; 24821</t>
+          <t>10670; 24433</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2332; 9346</t>
+          <t>2428; 9445</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>634; 7753</t>
+          <t>387; 6676</t>
         </is>
       </c>
     </row>
@@ -1576,42 +1576,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>36922</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>44894</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>31390</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>13729</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>21046</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>37951</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>16500</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>11019</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>36922</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>44894</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>31390</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>14746</t>
+          <t>10992</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>25765</t>
+          <t>24720</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14630; 28973</t>
+          <t>28954; 47674</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29146; 49528</t>
+          <t>35030; 56519</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10743; 23715</t>
+          <t>23798; 41168</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6204; 17037</t>
+          <t>8316; 20652</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>28141; 47135</t>
+          <t>14784; 28756</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35030; 56439</t>
+          <t>28635; 47623</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23405; 40687</t>
+          <t>11055; 24684</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9540; 22548</t>
+          <t>6294; 17420</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>47516; 70129</t>
+          <t>45635; 69415</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>69164; 98062</t>
+          <t>69583; 97652</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>37335; 59181</t>
+          <t>37106; 59586</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18146; 36541</t>
+          <t>17217; 34546</t>
         </is>
       </c>
     </row>
@@ -1784,42 +1784,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1852,42 +1852,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>6764</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>15899</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>6805</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>7382</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>10144</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>9708</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>4412</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>5051</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>6764</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>15899</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>6805</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7937</t>
+          <t>5068</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12988</t>
+          <t>12449</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5848; 16210</t>
+          <t>3324; 11978</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5282; 15416</t>
+          <t>10472; 23303</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1820; 8925</t>
+          <t>3287; 11711</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2304; 10100</t>
+          <t>3702; 14606</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3325; 11911</t>
+          <t>5951; 16878</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10192; 22899</t>
+          <t>5522; 16028</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3444; 12307</t>
+          <t>1818; 8456</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3905; 15791</t>
+          <t>2265; 10368</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11062; 24525</t>
+          <t>11132; 23684</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18478; 34730</t>
+          <t>18702; 35461</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6852; 17283</t>
+          <t>6885; 17468</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7546; 20873</t>
+          <t>7134; 20155</t>
         </is>
       </c>
     </row>
@@ -1992,42 +1992,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>26</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,42 +2060,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>46525</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>73377</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>40724</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>22251</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>35304</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>51712</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>23369</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>17151</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>46525</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>73377</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>40724</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>24034</t>
+          <t>17184</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>41185</t>
+          <t>39435</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>26187; 45694</t>
+          <t>36602; 58346</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>40579; 65077</t>
+          <t>59838; 86482</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17224; 31776</t>
+          <t>30622; 52365</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10971; 24898</t>
+          <t>14992; 32709</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>36863; 58823</t>
+          <t>26221; 45310</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>60991; 86973</t>
+          <t>41292; 63464</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31377; 52052</t>
+          <t>16176; 31456</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>16368; 35058</t>
+          <t>11559; 26023</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>67454; 96435</t>
+          <t>68004; 95812</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>108165; 143608</t>
+          <t>107258; 141274</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>52697; 76910</t>
+          <t>52656; 78791</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>30701; 52871</t>
+          <t>29367; 51370</t>
         </is>
       </c>
     </row>
